--- a/TESTS/zlit_5_tom_soier.xlsx
+++ b/TESTS/zlit_5_tom_soier.xlsx
@@ -507,7 +507,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H46"/>
+  <dimension ref="A1:I46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -561,6 +561,11 @@
           <t>Тип</t>
         </is>
       </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>ГР</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -580,7 +585,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Марк Твен — видатний американський письменник гуморист і сатирик</t>
+          <t>Марк Твен</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -601,6 +606,11 @@
       <c r="H2" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -622,7 +632,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Самюель Лонгхорн Клеменс — «Марк Твен» це літературний псевдонім</t>
+          <t>Самюель Лонгхорн Клеменс</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -643,6 +653,11 @@
       <c r="H3" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -664,7 +679,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>США — маленьке містечко Ганнібал на берегах Міссісіпі в середині XIX ст.</t>
+          <t>США</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -685,6 +700,11 @@
       <c r="H4" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -706,7 +726,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>З тіткою Поллі — він сирота і живе під її опікою разом з братом Сідом</t>
+          <t>З тіткою Поллі</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -727,6 +747,11 @@
       <c r="H5" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -748,7 +773,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Жвавим непосидою мрійником і вигадником — він не любить школу але сповнений фантазії і завзяття</t>
+          <t>Жвавим непосидою мрійником і вигадником</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -769,6 +794,11 @@
       <c r="H6" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -790,7 +820,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Суворо але любить — вона намагається виховати його але розуміє що він не злий а лише бешкетний</t>
+          <t>Суворо але любить</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -811,6 +841,11 @@
       <c r="H7" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -832,7 +867,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Том зробив вигляд що білення паркану — надзвичайне задоволення і переконав друзів платити за право поробити це</t>
+          <t>Том зробив вигляд що білення паркану</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -853,6 +888,11 @@
       <c r="H8" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -874,7 +914,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Різні цінні речі — яблуко жаб'ячу лапку намисто — друзі самі платили за роботу що він мав виконати</t>
+          <t>Різні цінні речі</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -895,6 +935,11 @@
       <c r="H9" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -916,7 +961,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Що люди хочуть того від чого їх відштовхують — зробити нудне завдання привабливим і всі захочуть це робити</t>
+          <t>Що люди хочуть того від чого їх відштовхують</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -937,6 +982,11 @@
       <c r="H10" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -948,37 +998,42 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>Питання 4 (варіант 1)</t>
+          <t>Хто така Бекі Тетчер для Тома Соєра?</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Його сестра</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Дівчинка, в яку Том влюбився одразу, щойно побачив у школі</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Учителька</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Сусідка-подруга тітки Поллі</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -990,37 +1045,42 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>Питання 4 (варіант 2)</t>
+          <t>Як Том намагався привернути увагу Бекі в школі?</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Ігнорував її</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Робив різні витребеньки й хитрощі, щоб вона його помітила</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Поскаржився вчителю</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Подарував їй гроші</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1032,37 +1092,42 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>Питання 4 (варіант 3)</t>
+          <t>Що сталося, коли вчитель випадково виявив зіпсований підручник і шукав винного?</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Том одразу зізнався</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Том зголосився взяти провину на себе, щоб урятувати Бекі від покарання</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Покарали весь клас</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Ніхто не зізнався, і про це забули</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1074,37 +1139,42 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Питання 5 (варіант 1)</t>
+          <t>Навіщо Том і Гекльберрі Фін вночі прийшли на кладовище?</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Щоб поховати кота</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Випробувати марновірний спосіб «лікування бородавок» котячим трупом</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Щоб когось налякати</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Заради сну на свіжому повітрі</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1116,37 +1186,42 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>Питання 5 (варіант 2)</t>
+          <t>Кого Том і Гек побачили на кладовищі тієї ночі?</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Привида</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Лікаря, Мафа Поттера та Індіанця Джо, що розкопували могилу</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Поліцію</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Нікого, було порожньо</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1158,37 +1233,42 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>Питання 5 (варіант 3)</t>
+          <t>Що сталося під час сварки на кладовищі, свідками якої стали хлопці?</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Усі мирно розійшлись</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Індіанець Джо вбив лікаря ножем Мафа Поттера</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Лікар утік</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Мафа Поттера заарештували одразу</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1200,37 +1280,42 @@
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>Питання 6 (варіант 1)</t>
+          <t>Чому Том і Гек поклялися нікому не розповідати про побачене вбивство?</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Їм наказали дорослі</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Вони боялися, що Індіанець Джо вб'є і їх, якщо дізнається про свідків</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Їм було байдуже</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Вони не зрозуміли, що сталось</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1242,37 +1327,42 @@
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>Питання 6 (варіант 2)</t>
+          <t>Яким чином Том і Гек скріпили свою клятву мовчання?</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Усно домовились і забули</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Написали клятву кров'ю і поклялися мовчати під страхом смерті</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Підписали папір у вчителя</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Розповіли тітці Поллі під секретом</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1284,37 +1374,42 @@
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>Питання 6 (варіант 3)</t>
+          <t>Кого звинуватили у вбивстві лікаря, поки правда не була відома?</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Індіанця Джо одразу</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>П'яницю Мафа Поттера, який нічого не пам'ятав про ту ніч</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Самого Тома</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Нікого не звинуватили</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1326,37 +1421,42 @@
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>Питання 7 (варіант 1)</t>
+          <t>Куди втекли Том, Гек і Джо Гарпер, щоб «стати піратами»?</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>У сусіднє місто</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>На безлюдний острів посеред річки Міссісіпі</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>У ліс за містом</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>До родичів в інше село</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1368,37 +1468,42 @@
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>Питання 7 (варіант 2)</t>
+          <t>Як містечко відреагувало, коли хлопці зникли і всі думали, що вони загинули у річці?</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Ніхто не помітив</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>У містечку оголосили жалобу й готувались до похорону хлопців</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Усі одразу почали шукати їх на острові</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Поліція швидко їх знайшла</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1410,37 +1515,42 @@
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>Питання 7 (варіант 3)</t>
+          <t>Що Том зробив, дізнавшись про підготовку до власного «похорону»?</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Залишився на острові назавжди</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Таємно повернувся додому вночі, а потім влаштував з друзями ефектну появу на власних поминках</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Написав листа тітці</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Послав звістку через Гека</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1452,37 +1562,42 @@
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>Питання 8 (варіант 1)</t>
+          <t>Чому Тома мучило сумління щодо суду над Мафом Поттером?</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Йому було байдуже до суду</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Він знав правду про справжнього вбивцю, але боявся Індіанця Джо й мовчав</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Він сам хотів стати свідком заради слави</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Він не розумів, що відбувається на суді</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1494,37 +1609,42 @@
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>Питання 8 (варіант 2)</t>
+          <t>Що Том врешті зробив на суді, попри страх перед Індіанцем Джо?</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Промовчав до кінця</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Зважився і свідчив правду, назвавши справжнього вбивцю</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Втік із залу суду</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Збрехав на користь Мафа</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1536,37 +1656,42 @@
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>Питання 8 (варіант 3)</t>
+          <t>Що сталося з Індіанцем Джо одразу після слів Тома на суді?</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Його заарештували одразу</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Він вистрибнув у вікно і втік із залу суду</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Він зізнався сам</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Він напав на Тома прямо в суді</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1578,37 +1703,42 @@
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>Питання 9 (варіант 1)</t>
+          <t>Чому Том і Бекі заблукали в печері під час шкільного пікніка?</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Їх там залишили навмисно</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Вони відійшли від групи, досліджуючи бічні ходи, і не змогли знайти дорогу назад</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Стався землетрус</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Печеру закрили навмисно</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1620,37 +1750,42 @@
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>Питання 9 (варіант 2)</t>
+          <t>Кого Том випадково побачив у глибині печери, ховаючись від Бекі, щоб не лякати її?</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Лікаря</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Індіанця Джо, що теж переховувався в печері</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Привида</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Гека Фінна</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1662,37 +1797,42 @@
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>Питання 9 (варіант 3)</t>
+          <t>Як Тому і Бекі вдалося врятуватися з печери?</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Їх знайшли одразу</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Том знайшов вихід, повзучи на світло, далеко від основного входу, який завалили</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Індіанець Джо їх відпустив</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Вони прокопали хід самі</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1704,37 +1844,42 @@
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>Питання 10 (варіант 1)</t>
+          <t>Що Том і Гек знайшли в печері після того, як Індіанець Джо загинув там, замкнений?</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Нічого</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Скарб золотих монет, який колись заховав там Індіанець Джо</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Старі книги</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Зброю</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1746,37 +1891,42 @@
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>Питання 10 (варіант 2)</t>
+          <t>Що сталося зі знайденим золотом наприкінці книги?</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Його забрали в місто</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Його поклали під відсотки в банк, і Том із Геком стали найбагатшими дітьми містечка</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Його закопали знову</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Його віддали поліції</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1788,37 +1938,42 @@
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>Питання 10 (варіант 3)</t>
+          <t>Як Гек поставився до свого нового багатства й «пристойного» життя, яке йому нав'язали?</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Був дуже задоволений одразу</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Йому було тісно й нудно в новому пристойному житті, і він тікав назад до старих звичок</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Він роздав усе гроші</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Він поїхав із містечка назавжди</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1843,8 +1998,6 @@
           <t>Хибно</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr"/>
-      <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr">
         <is>
           <t>А</t>
@@ -1853,6 +2006,11 @@
       <c r="H32" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1877,8 +2035,6 @@
           <t>Хибно</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr"/>
-      <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr">
         <is>
           <t>Б</t>
@@ -1887,6 +2043,11 @@
       <c r="H33" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1911,8 +2072,6 @@
           <t>Хибно</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr"/>
-      <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr">
         <is>
           <t>А</t>
@@ -1921,6 +2080,11 @@
       <c r="H34" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1932,21 +2096,19 @@
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>Яка риса американського дитинства відображена у книзі?</t>
+          <t>У «Пригодах Тома Соєра» Марк Твен відображає власні дитячі спогади про життя на берегах Міссісіпі.</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Так</t>
+          <t>Правда</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Ні</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr"/>
-      <c r="F35" t="inlineStr"/>
+          <t>Хибно</t>
+        </is>
+      </c>
       <c r="G35" t="inlineStr">
         <is>
           <t>А</t>
@@ -1955,6 +2117,11 @@
       <c r="H35" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1966,29 +2133,32 @@
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>Ким є Бекі Тетчер у сюжеті?</t>
+          <t>Бекі Тетчер у книзі — найкращий друг Тома, разом із яким він шукає скарби.</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Так</t>
+          <t>Правда</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Ні</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr"/>
-      <c r="F36" t="inlineStr"/>
+          <t>Хибно</t>
+        </is>
+      </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -2000,21 +2170,19 @@
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>Що автобіографічного є у «Пригодах Тома Соєра»?</t>
+          <t>У книзі показано типове для американського містечка XIX століття дитинство — зі школою, церквою і вуличними пригодами.</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Так</t>
+          <t>Правда</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Ні</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr"/>
-      <c r="F37" t="inlineStr"/>
+          <t>Хибно</t>
+        </is>
+      </c>
       <c r="G37" t="inlineStr">
         <is>
           <t>А</t>
@@ -2023,6 +2191,11 @@
       <c r="H37" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -2034,21 +2207,19 @@
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>Яке велике відкриття зробили Том і Гек у печері?</t>
+          <t>У печері Том і Гек знайшли скарб золота, захований Індіанцем Джо.</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Так</t>
+          <t>Правда</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Ні</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr"/>
-      <c r="F38" t="inlineStr"/>
+          <t>Хибно</t>
+        </is>
+      </c>
       <c r="G38" t="inlineStr">
         <is>
           <t>А</t>
@@ -2057,6 +2228,11 @@
       <c r="H38" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -2068,29 +2244,32 @@
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>Що трапилось з Томом і Бекі Тетчер у печері?</t>
+          <t>Том і Бекі заблукали в печері, але вийшли через основний вхід, де на них чекали дорослі.</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Так</t>
+          <t>Правда</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Ні</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr"/>
-      <c r="F39" t="inlineStr"/>
+          <t>Хибно</t>
+        </is>
+      </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -2102,21 +2281,19 @@
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>Яка головна ідея «Пригод Тома Соєра»?</t>
+          <t>Головна ідея книги — дитяча вигадливість, дружба і сміливість здатні подолати найбільші небезпеки.</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Так</t>
+          <t>Правда</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Ні</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr"/>
-      <c r="F40" t="inlineStr"/>
+          <t>Хибно</t>
+        </is>
+      </c>
       <c r="G40" t="inlineStr">
         <is>
           <t>А</t>
@@ -2125,6 +2302,11 @@
       <c r="H40" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -2169,6 +2351,11 @@
           <t>multiple</t>
         </is>
       </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>ГР2</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2211,6 +2398,11 @@
           <t>multiple</t>
         </is>
       </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>ГР2</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -2220,27 +2412,27 @@
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>Які пригоди пережили Том і його друзі?</t>
+          <t>Які пригоди пережив Том у печері та довкола неї?</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Стали свідками вбивства</t>
+          <t>Заблукав там разом із Бекі</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Заблукали у печері</t>
+          <t>Побачив Індіанця Джо</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Відкрили школу</t>
+          <t>Знайшов школу</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Знайшли скарб злочинця</t>
+          <t>Пізніше знайшов скарб золота</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -2251,6 +2443,11 @@
       <c r="H43" t="inlineStr">
         <is>
           <t>multiple</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -2272,7 +2469,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Найкращий друг Тома — вільний безпритульний хлопець якому всі заздрять бо він не ходить до школи</t>
+          <t>Найкращий друг Тома</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -2293,6 +2490,11 @@
       <c r="H44" t="inlineStr">
         <is>
           <t>multiple</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -2314,7 +2516,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Вбивства яке вчинив Індіанець Джо — і цей жах переслідував їх протягом усього сюжету</t>
+          <t>Вбивства яке вчинив Індіанець Джо</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -2335,6 +2537,11 @@
       <c r="H45" t="inlineStr">
         <is>
           <t>multiple</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -2356,7 +2563,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Вони боялись Індіанця Джо — він здавався безжалісним злочинцем і вони страшились помсти</t>
+          <t>Вони боялись Індіанця Джо</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -2377,6 +2584,11 @@
       <c r="H46" t="inlineStr">
         <is>
           <t>multiple</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
